--- a/jadwal_shift.xlsx
+++ b/jadwal_shift.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="14">
   <si>
     <t xml:space="preserve">Tanggal</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">tri.sutrisno@erajaya.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelia.pebriani@erajaya.com</t>
   </si>
 </sst>
 </file>
@@ -143,8 +146,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -352,482 +359,482 @@
   <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="52.48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46253</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>46253</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>46253</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>46254</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>46254</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46254</v>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="B10" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>46256</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46256</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="B12" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>46256</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>46257</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>46257</v>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="B15" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>46257</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="B16" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46258</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>46258</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="B18" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>46258</v>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>0.5625</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <v>0.5625</v>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>46260</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <v>0.375</v>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D24" s="1" t="s">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C25" s="3" t="n">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>8</v>
       </c>
     </row>
